--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>продана</t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="шахматка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="шахматка" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>продана</t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D143" s="3" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D153" s="3" t="n">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D163" s="3" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D165" s="3" t="n">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D169" s="3" t="n">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D171" s="3" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D173" s="3" t="n">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D175" s="3" t="n">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D177" s="3" t="n">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D181" s="3" t="n">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D189" s="3" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D263" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободна </t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -5382,7 +5382,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>бронь</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D221" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D191" s="3" t="n">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D267" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>продана</t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D215" s="3" t="n">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D235" s="3" t="n">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D245" s="3" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D275" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>бронь</t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D239" s="3" t="n">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D233" s="3" t="n">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>продана</t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D235" s="3" t="n">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>продана</t>
+          <t>свободна</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">

--- a/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/jk_data.xlsx
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>бронь</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D227" s="3" t="n">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D229" s="3" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D235" s="3" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D237" s="3" t="n">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>бронь</t>
         </is>
       </c>
       <c r="D257" s="3" t="n">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D269" s="3" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>свободна</t>
+          <t>продана</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
